--- a/documentation_files/documentation_tables.xlsx
+++ b/documentation_files/documentation_tables.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa.sharepoint.com/sites/DFW-TeamR6CoastalShellfish-RecCrabData/Shared Documents/02_code/Freshwater-creel-estimation-method/documentation_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/matthew_george_dfw_wa_gov/Documents/Desktop/Github/FWC-estimation-method/documentation_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="644" documentId="13_ncr:1_{06BDCB52-A10A-4652-9501-BAA58E581D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90BE282F-20EF-41D8-9E98-3FAF35BE5EE8}"/>
+  <xr:revisionPtr revIDLastSave="646" documentId="13_ncr:1_{06BDCB52-A10A-4652-9501-BAA58E581D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40010EDC-B4C3-422A-860B-12053F09E1A5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{D87A213F-20EA-453F-96F1-E2F9D588DE08}"/>
   </bookViews>
@@ -940,9 +940,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1953,71 +1952,68 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="130" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="1"/>
-    <col min="4" max="4" width="19.28515625" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="130" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2033,9 +2029,9 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="62.42578125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="52.140625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="119.85546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="62.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="52.140625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="119.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2043,13 +2039,13 @@
       <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2057,13 +2053,13 @@
       <c r="A2" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>193</v>
       </c>
     </row>
@@ -2071,13 +2067,13 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2085,13 +2081,13 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2099,13 +2095,13 @@
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2113,13 +2109,13 @@
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2127,13 +2123,13 @@
       <c r="A7" t="s">
         <v>252</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>261</v>
       </c>
     </row>
@@ -2141,13 +2137,13 @@
       <c r="A8" t="s">
         <v>253</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>265</v>
       </c>
     </row>
@@ -2155,13 +2151,13 @@
       <c r="A9" t="s">
         <v>254</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>269</v>
       </c>
     </row>
@@ -2169,13 +2165,13 @@
       <c r="A10" t="s">
         <v>255</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>262</v>
       </c>
     </row>
@@ -2183,13 +2179,13 @@
       <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2197,13 +2193,13 @@
       <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2211,13 +2207,13 @@
       <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>130</v>
       </c>
     </row>
@@ -2225,13 +2221,13 @@
       <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>133</v>
       </c>
     </row>
@@ -2239,13 +2235,13 @@
       <c r="A15" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <v>0.5</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2253,13 +2249,13 @@
       <c r="A16" t="s">
         <v>194</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>203</v>
       </c>
     </row>
@@ -2267,13 +2263,13 @@
       <c r="A17" t="s">
         <v>197</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>199</v>
       </c>
     </row>
@@ -2281,13 +2277,13 @@
       <c r="A18" t="s">
         <v>256</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>268</v>
       </c>
     </row>
@@ -2512,10 +2508,10 @@
       <c r="A2" t="s">
         <v>214</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>44422</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>44561</v>
       </c>
     </row>
@@ -2523,10 +2519,10 @@
       <c r="A3" t="s">
         <v>215</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>44751</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>44804</v>
       </c>
     </row>
@@ -2534,10 +2530,10 @@
       <c r="A4" t="s">
         <v>216</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>44562</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>44620</v>
       </c>
     </row>
@@ -2545,10 +2541,10 @@
       <c r="A5" t="s">
         <v>217</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>44709</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>44752</v>
       </c>
     </row>
@@ -2556,10 +2552,10 @@
       <c r="A6" t="s">
         <v>218</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>44348</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>44392</v>
       </c>
     </row>
@@ -2567,10 +2563,10 @@
       <c r="A7" t="s">
         <v>219</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>44713</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>44757</v>
       </c>
     </row>
@@ -2578,10 +2574,10 @@
       <c r="A8" t="s">
         <v>220</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>44682</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>44712</v>
       </c>
     </row>
@@ -2589,10 +2585,10 @@
       <c r="A9" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>44345</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>44395</v>
       </c>
     </row>
@@ -2600,10 +2596,10 @@
       <c r="A10" t="s">
         <v>222</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>44562</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>44620</v>
       </c>
     </row>
@@ -2611,10 +2607,10 @@
       <c r="A11" t="s">
         <v>223</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>44743</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>44880</v>
       </c>
     </row>
@@ -2622,10 +2618,10 @@
       <c r="A12" t="s">
         <v>224</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>44789</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>44834</v>
       </c>
     </row>
@@ -2633,10 +2629,10 @@
       <c r="A13" t="s">
         <v>225</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>44757</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>44804</v>
       </c>
     </row>
@@ -2644,10 +2640,10 @@
       <c r="A14" t="s">
         <v>226</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <v>44805</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>44910</v>
       </c>
     </row>
@@ -2655,10 +2651,10 @@
       <c r="A15" t="s">
         <v>227</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>44728</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>44771</v>
       </c>
     </row>
@@ -2666,10 +2662,10 @@
       <c r="A16" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>44531</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>44607</v>
       </c>
     </row>
@@ -2677,10 +2673,10 @@
       <c r="A17" t="s">
         <v>229</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>44805</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>44957</v>
       </c>
     </row>
@@ -2688,10 +2684,10 @@
       <c r="A18" t="s">
         <v>230</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="5">
         <v>44228</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>44301</v>
       </c>
     </row>
@@ -2699,10 +2695,10 @@
       <c r="A19" t="s">
         <v>231</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="5">
         <v>44709</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>44804</v>
       </c>
     </row>
@@ -2710,10 +2706,10 @@
       <c r="A20" t="s">
         <v>232</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="5">
         <v>44835</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>44972</v>
       </c>
     </row>
@@ -2721,10 +2717,10 @@
       <c r="A21" t="s">
         <v>233</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>44820</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>44895</v>
       </c>
     </row>
@@ -2732,10 +2728,10 @@
       <c r="A22" t="s">
         <v>234</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="5">
         <v>44805</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>44895</v>
       </c>
     </row>
@@ -2743,10 +2739,10 @@
       <c r="A23" t="s">
         <v>235</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>44455</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>44530</v>
       </c>
     </row>
@@ -2754,10 +2750,10 @@
       <c r="A24" t="s">
         <v>236</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="5">
         <v>44348</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <v>44392</v>
       </c>
     </row>
@@ -2765,10 +2761,10 @@
       <c r="A25" t="s">
         <v>237</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="5">
         <v>44713</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <v>44757</v>
       </c>
     </row>
@@ -2776,10 +2772,10 @@
       <c r="A26" t="s">
         <v>238</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="5">
         <v>44896</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <v>44972</v>
       </c>
     </row>
@@ -2787,10 +2783,10 @@
       <c r="A27" t="s">
         <v>239</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="5">
         <v>44896</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>44972</v>
       </c>
     </row>
@@ -2798,10 +2794,10 @@
       <c r="A28" t="s">
         <v>240</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="5">
         <v>44896</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="5">
         <v>44957</v>
       </c>
     </row>
@@ -2809,10 +2805,10 @@
       <c r="A29" t="s">
         <v>241</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="5">
         <v>44531</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <v>44592</v>
       </c>
     </row>
@@ -2820,10 +2816,10 @@
       <c r="A30" t="s">
         <v>242</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="5">
         <v>44583</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="5">
         <v>44607</v>
       </c>
     </row>
@@ -2831,10 +2827,10 @@
       <c r="A31" t="s">
         <v>243</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="5">
         <v>44562</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>44592</v>
       </c>
     </row>
@@ -2842,10 +2838,10 @@
       <c r="A32" t="s">
         <v>244</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="5">
         <v>44911</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="5">
         <v>45016</v>
       </c>
     </row>
@@ -2853,10 +2849,10 @@
       <c r="A33" t="s">
         <v>245</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="5">
         <v>44911</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>45016</v>
       </c>
     </row>
@@ -2864,10 +2860,10 @@
       <c r="A34" t="s">
         <v>246</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B34" s="5">
         <v>44835</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="5">
         <v>44911</v>
       </c>
     </row>
@@ -2875,10 +2871,10 @@
       <c r="A35" t="s">
         <v>247</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="5">
         <v>44805</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="5">
         <v>44911</v>
       </c>
     </row>
@@ -2886,10 +2882,10 @@
       <c r="A36" t="s">
         <v>248</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="5">
         <v>44820</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="5">
         <v>44911</v>
       </c>
     </row>
@@ -2897,10 +2893,10 @@
       <c r="A37" t="s">
         <v>249</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37" s="5">
         <v>44910</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="5">
         <v>45016</v>
       </c>
     </row>
@@ -2908,10 +2904,10 @@
       <c r="A38" t="s">
         <v>250</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="5">
         <v>44927</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="5">
         <v>44957</v>
       </c>
     </row>
@@ -2919,10 +2915,10 @@
       <c r="A39" t="s">
         <v>251</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="5">
         <v>44958</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="5">
         <v>45031</v>
       </c>
     </row>
@@ -2952,7 +2948,7 @@
       <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3143,7 +3139,7 @@
       <c r="A7" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3356,15 +3352,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100812E8DC5201BA846851ED74C3E1B5852" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4fda3defcfeb6d1244c6136f96db2c76">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="9675aba4-d3b2-4750-a385-9de1110e9966" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4ecd7dc06ce3a22b9b72c30878c236cf" ns1:_="" ns2:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -3553,6 +3540,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{680AFC83-00EF-41F8-A235-84A3712529D9}">
   <ds:schemaRefs>
@@ -3565,6 +3561,25 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1460C081-765F-4244-81B2-D050FFCA0575}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9675aba4-d3b2-4750-a385-9de1110e9966"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67CC9E58-A710-4997-A48D-4B2D5C492AA2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -3572,10 +3587,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1460C081-765F-4244-81B2-D050FFCA0575}"/>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{45011977-b912-4387-97a4-f4c94a801377}" enabled="1" method="Standard" siteId="{11d0e217-264e-400a-8ba0-57dcc127d72d}" removed="0"/>
